--- a/AtchisonRegime/Outputs/Euro/df_regInflation_Euro.xlsx
+++ b/AtchisonRegime/Outputs/Euro/df_regInflation_Euro.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H377"/>
+  <dimension ref="A1:H378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10205,22 +10205,22 @@
         <v>45716</v>
       </c>
       <c r="B376" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="C376" t="n">
-        <v>2.466666666666667</v>
+        <v>2.4</v>
       </c>
       <c r="D376" t="n">
-        <v>5.241666666666666</v>
+        <v>5.236111111111111</v>
       </c>
       <c r="E376" t="n">
-        <v>2.990496853128501</v>
+        <v>2.995916533052266</v>
       </c>
       <c r="F376" t="b">
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>-0.9279394482883139</v>
+        <v>-0.9466589205079275</v>
       </c>
       <c r="H376" t="b">
         <v>0</v>
@@ -10231,24 +10231,50 @@
         <v>45747</v>
       </c>
       <c r="B377" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="C377" t="n">
-        <v>2.433333333333333</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="D377" t="n">
-        <v>5.100000000000001</v>
+        <v>5.091666666666667</v>
       </c>
       <c r="E377" t="n">
-        <v>3.006089058656024</v>
+        <v>3.01390823635075</v>
       </c>
       <c r="F377" t="b">
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>-0.8870883778336536</v>
+        <v>-0.9152014981959544</v>
       </c>
       <c r="H377" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B378" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C378" t="n">
+        <v>2.233333333333333</v>
+      </c>
+      <c r="D378" t="n">
+        <v>4.944444444444445</v>
+      </c>
+      <c r="E378" t="n">
+        <v>3.022340100408905</v>
+      </c>
+      <c r="F378" t="b">
+        <v>0</v>
+      </c>
+      <c r="G378" t="n">
+        <v>-0.8970238361805523</v>
+      </c>
+      <c r="H378" t="b">
         <v>0</v>
       </c>
     </row>
